--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_202_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_202_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6156</v>
+        <v>5.2891</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7044</v>
+        <v>2.1762</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9112</v>
+        <v>3.1129</v>
       </c>
       <c r="G2" t="n">
         <v>5.4428</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0411</v>
+        <v>-0.3677</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3022</v>
+        <v>-0.1006</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1988</v>
+        <v>4.6781</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5096000000000001</v>
+        <v>1.0561</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6892</v>
+        <v>3.622</v>
       </c>
       <c r="G3" t="n">
         <v>2.0588</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2337</v>
+        <v>0.2456</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8136</v>
+        <v>-0.2671</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5799</v>
+        <v>0.5127</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7215</v>
+        <v>2.2279</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1917</v>
+        <v>-0.5777</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5298</v>
+        <v>2.8057</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6751</v>
+        <v>0.3552</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2065</v>
+        <v>-0.8894</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4685</v>
+        <v>1.2446</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5815</v>
+        <v>-0.4914</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2134</v>
+        <v>-0.6351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.368</v>
+        <v>0.1437</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0936</v>
+        <v>0.8466</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9931</v>
+        <v>-0.2543</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1005</v>
+        <v>1.1009</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6547</v>
+        <v>0.0688</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3214</v>
+        <v>-0.0863</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3333</v>
+        <v>0.1551</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.2166</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1127</v>
+        <v>2.2203</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6765</v>
+        <v>2.5153</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5639</v>
+        <v>-0.295</v>
       </c>
       <c r="G5" t="n">
         <v>3.3044</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1125</v>
+        <v>0.2201</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.0277</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0764</v>
+        <v>0.1924</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6724</v>
+        <v>1.8676</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9316</v>
+        <v>1.0436</v>
       </c>
       <c r="F6" t="n">
-        <v>2.604</v>
+        <v>0.824</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3552</v>
+        <v>2.6751</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8894</v>
+        <v>2.2065</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2446</v>
+        <v>0.4685</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4914</v>
+        <v>1.5815</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6351</v>
+        <v>1.2134</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1437</v>
+        <v>0.368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8466</v>
+        <v>1.0936</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2543</v>
+        <v>0.9931</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1009</v>
+        <v>0.1005</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4867</v>
+        <v>0.8008</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>0.1733</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0466</v>
+        <v>0.6276</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2836</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6432</v>
+        <v>1.2894</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2101</v>
+        <v>-0.1438</v>
       </c>
       <c r="F7" t="n">
         <v>1.4332</v>
@@ -1000,10 +1000,10 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2987</v>
+        <v>-0.0551</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4208</v>
+        <v>0.067</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1221</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2229</v>
+        <v>0.7598</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9275</v>
+        <v>1.4307</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7045</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>1.5385</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4573</v>
+        <v>0.0795</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3943</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1638</v>
+        <v>-0.2252</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6817</v>
+        <v>1.5951</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5179</v>
+        <v>-1.8203</v>
       </c>
       <c r="G9" t="n">
         <v>1.5723</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5373</v>
+        <v>0.1483</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>0.1024</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3484</v>
+        <v>0.0459</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1737</v>
+        <v>-0.4432</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8793</v>
+        <v>0.6434</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.053</v>
+        <v>-1.0866</v>
       </c>
       <c r="G10" t="n">
         <v>-1.012</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7481</v>
+        <v>0.4786</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7117</v>
+        <v>0.4758</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3478</v>
+        <v>-0.9028</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2794</v>
+        <v>0.0312</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0684</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5175</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.1533</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7107</v>
+        <v>-1.6099</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6734</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0373</v>
+        <v>-0.9365</v>
       </c>
       <c r="G12" t="n">
         <v>0.0854</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4714</v>
+        <v>-0.3705</v>
       </c>
       <c r="T12" t="n">
         <v>-0.224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3247</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8588</v>
+        <v>-3.1442</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9605</v>
+        <v>-0.414</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8983</v>
+        <v>-2.7303</v>
       </c>
       <c r="G13" t="n">
         <v>0.1481</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2208</v>
+        <v>-0.5063</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>-0.275</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3993</v>
+        <v>-0.2313</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.2599</v>
+        <v>12.0069</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9359</v>
+        <v>8.682700000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>3.324100000000002</v>
+        <v>3.3242</v>
       </c>
       <c r="G14" t="n">
         <v>18.5317</v>
@@ -1546,13 +1546,13 @@
         <v>13.9171</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1580000000000004</v>
+        <v>0.5888</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1774</v>
+        <v>-0.4303</v>
       </c>
       <c r="U14" t="n">
-        <v>1.019399999999999</v>
+        <v>1.0193</v>
       </c>
       <c r="V14" t="n">
         <v>-4.7938</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3903</v>
+        <v>5.0364</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8221</v>
+        <v>4.4682</v>
       </c>
       <c r="F15" t="n">
         <v>0.5682</v>
@@ -1624,10 +1624,10 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6528</v>
+        <v>0.2989</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3857</v>
+        <v>0.0318</v>
       </c>
       <c r="U15" t="n">
         <v>0.2671</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.619</v>
+        <v>3.8563</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0829</v>
+        <v>2.7906</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5361</v>
+        <v>1.0656</v>
       </c>
       <c r="G16" t="n">
         <v>0.4543</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.036</v>
+        <v>0.2732</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0376</v>
+        <v>-0.3299</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0737</v>
+        <v>0.6032</v>
       </c>
       <c r="V16" t="n">
         <v>1.0412</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5263</v>
+        <v>2.2676</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4341</v>
+        <v>2.1418</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1259</v>
       </c>
       <c r="G17" t="n">
         <v>1.9419</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8975</v>
+        <v>-0.1562</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9709</v>
+        <v>-0.2631</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6778999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.595</v>
+        <v>0.4599</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6181</v>
+        <v>1.3822</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0231</v>
+        <v>-0.9223</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1301</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1331</v>
+        <v>-0.2682</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.094</v>
+        <v>-0.3299</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0391</v>
+        <v>0.0617</v>
       </c>
       <c r="V18" t="n">
         <v>1.4665</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9761</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.194</v>
+        <v>-0.076</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7821</v>
+        <v>-0.4568</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9258999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4266</v>
+        <v>0.0167</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2025</v>
+        <v>0.1228</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2942</v>
+        <v>-1.3735</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3833</v>
+        <v>0.9115</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6775</v>
+        <v>-2.285</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7279</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3615</v>
+        <v>0.2822</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4604</v>
+        <v>-0.0114</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0988</v>
+        <v>0.2937</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0084</v>
+        <v>-2.6939</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5059</v>
+        <v>-1.4495</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5025</v>
+        <v>-1.2444</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4967</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7383</v>
+        <v>1.0528</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7695</v>
+        <v>0.8259</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0312</v>
+        <v>0.2269</v>
       </c>
       <c r="V21" t="n">
         <v>0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9779</v>
+        <v>-5.5606</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9276</v>
+        <v>-3.1635</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0503</v>
+        <v>-2.3971</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1623</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.973</v>
+        <v>0.3903</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3857</v>
+        <v>0.1498</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5874</v>
+        <v>0.2405</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7886</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3185</v>
+        <v>-5.6393</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0048</v>
+        <v>-4.651</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3137</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8845</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.2034</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5816</v>
+        <v>-0.2278</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3009</v>
+        <v>0.0244</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8157</v>
+        <v>-6.2938</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0323</v>
+        <v>-5.6784</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7834</v>
+        <v>-0.6153</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0879</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2639</v>
+        <v>-0.742</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1123</v>
+        <v>-0.7585</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1516</v>
+        <v>0.0165</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.2602</v>
+        <v>-10.4737</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3241</v>
+        <v>-3.324099999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.935999999999999</v>
+        <v>-7.1496</v>
       </c>
       <c r="G25" t="n">
         <v>-18.5315</v>
@@ -2404,13 +2404,13 @@
         <v>16.2366</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1579000000000002</v>
+        <v>0.9442999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0191</v>
+        <v>-1.0192</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1775</v>
+        <v>1.9638</v>
       </c>
       <c r="V25" t="n">
         <v>4.793900000000001</v>
